--- a/www/ig/fhir/sdo/CodeSystem-input-task-sdo-codesystem.xlsx
+++ b/www/ig/fhir/sdo/CodeSystem-input-task-sdo-codesystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.0.6</t>
+    <t>4.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T14:22:03+00:00</t>
+    <t>2026-06-29T08:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
